--- a/Table/Datas/MonsterData.xlsx
+++ b/Table/Datas/MonsterData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Unreal\ProjectH\Table\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1886BDAA-9FB1-4DC1-8222-881E5F1AD570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C085993E-CDAD-42EB-8372-AB76CF37A5D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
   <si>
     <t>!Field</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -84,6 +84,10 @@
   </si>
   <si>
     <t>SkillNos</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2005, 2006</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -176,7 +180,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -563,8 +567,8 @@
       <c r="D6" s="3">
         <v>102</v>
       </c>
-      <c r="E6" s="5">
-        <v>2005</v>
+      <c r="E6" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>6</v>
